--- a/data/trans_bre/P16A12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,12</t>
+          <t>-3,58; 0,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,79</t>
+          <t>-2,79; 2,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,23</t>
+          <t>-3,94; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,03</t>
+          <t>-2,84; 2,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 22,61</t>
+          <t>-49,79; 19,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 50,73</t>
+          <t>-34,31; 48,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 29,88</t>
+          <t>-35,59; 29,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 25,33</t>
+          <t>-25,82; 24,66</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,76</t>
+          <t>-1,11; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,89</t>
+          <t>-0,98; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,0</t>
+          <t>-2,83; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,64</t>
+          <t>-1,43; 4,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 73,64</t>
+          <t>-14,29; 76,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 70,92</t>
+          <t>-11,84; 69,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 29,32</t>
+          <t>-31,79; 27,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 112,86</t>
+          <t>-16,48; 120,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,8</t>
+          <t>-1,17; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,7</t>
+          <t>-0,82; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,57</t>
+          <t>-4,37; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -0,86</t>
+          <t>-6,85; -0,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 105,13</t>
+          <t>-21,19; 103,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 93,3</t>
+          <t>-9,72; 99,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 21,71</t>
+          <t>-41,91; 20,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,22; -12,93</t>
+          <t>-71,52; -12,8</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,33</t>
+          <t>-1,45; 2,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,43</t>
+          <t>-2,01; 3,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,57</t>
+          <t>-1,85; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; -0,43</t>
+          <t>-4,91; -0,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 55,87</t>
+          <t>-24,72; 50,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 44,97</t>
+          <t>-19,67; 44,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 42,73</t>
+          <t>-22,21; 45,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,87; -5,33</t>
+          <t>-45,49; -6,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,62</t>
+          <t>-0,7; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,14; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,79</t>
+          <t>-1,85; 0,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,55</t>
+          <t>-2,71; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 31,06</t>
+          <t>-11,46; 32,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 36,34</t>
+          <t>-1,72; 38,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 10,53</t>
+          <t>-20,08; 11,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 5,28</t>
+          <t>-30,4; 9,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A12-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,46%</t>
+          <t>-4,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,99</t>
+          <t>-3,95; 0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,83</t>
+          <t>-2,46; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,32</t>
+          <t>-4,38; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,09</t>
+          <t>-2,88; 1,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 19,16</t>
+          <t>-52,37; 19,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 48,58</t>
+          <t>-30,57; 52,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 29,6</t>
+          <t>-38,36; 27,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 24,66</t>
+          <t>-26,23; 24,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>-8,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,95</t>
+          <t>-0,77; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,77</t>
+          <t>-0,79; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,85</t>
+          <t>-2,75; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,55</t>
+          <t>-2,7; 1,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 76,87</t>
+          <t>-11,64; 76,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 69,82</t>
+          <t>-10,73; 71,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 27,52</t>
+          <t>-31,49; 35,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 120,63</t>
+          <t>-28,66; 19,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-1,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-41,76%</t>
+          <t>-24,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,72</t>
+          <t>-0,82; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,87</t>
+          <t>-0,76; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,56</t>
+          <t>-4,44; 1,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,87</t>
+          <t>-4,36; 0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 103,75</t>
+          <t>-16,3; 106,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 99,5</t>
+          <t>-9,51; 94,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 20,68</t>
+          <t>-40,32; 22,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,52; -12,8</t>
+          <t>-46,16; 4,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,64%</t>
+          <t>-20,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,14</t>
+          <t>-1,6; 2,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,51</t>
+          <t>-2,31; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,81</t>
+          <t>-2,09; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,54</t>
+          <t>-3,76; 0,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 50,52</t>
+          <t>-26,62; 49,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 44,44</t>
+          <t>-21,62; 44,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 45,26</t>
+          <t>-25,7; 46,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,49; -6,87</t>
+          <t>-36,78; 2,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-14,96%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,67</t>
+          <t>-0,69; 1,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,54</t>
+          <t>-0,22; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,9</t>
+          <t>-1,75; 1,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,68</t>
+          <t>-2,34; -0,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 32,72</t>
+          <t>-11,07; 29,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 38,14</t>
+          <t>-2,67; 36,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 11,79</t>
+          <t>-19,65; 14,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,49</t>
+          <t>-24,5; -2,26</t>
         </is>
       </c>
     </row>
